--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N107_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N107_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.72011984737111</v>
+        <v>5.642019475197805</v>
       </c>
       <c r="D2" t="n">
-        <v>26.55652374448714</v>
+        <v>4.315435108479161</v>
       </c>
       <c r="E2" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F2" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.08972426514821</v>
+        <v>2.939580193086585</v>
       </c>
       <c r="D3" t="n">
-        <v>24.92068583659804</v>
+        <v>4.049611448447181</v>
       </c>
       <c r="E3" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F3" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.16205512537677</v>
+        <v>3.113833957873725</v>
       </c>
       <c r="D4" t="n">
-        <v>11.05047961439865</v>
+        <v>1.795702937339781</v>
       </c>
       <c r="E4" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F4" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.2323268019594</v>
+        <v>1.662753105318403</v>
       </c>
       <c r="D5" t="n">
-        <v>28.25505515510675</v>
+        <v>4.591446462704847</v>
       </c>
       <c r="E5" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F5" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.34086028928729</v>
+        <v>5.417889797009185</v>
       </c>
       <c r="D6" t="n">
-        <v>27.09379530111666</v>
+        <v>4.402741736431457</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F6" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.996188437970746</v>
+        <v>1.624380621170246</v>
       </c>
       <c r="D7" t="n">
-        <v>40.47676577978902</v>
+        <v>6.577474439215716</v>
       </c>
       <c r="E7" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F7" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.59070584803412</v>
+        <v>2.858489700305545</v>
       </c>
       <c r="D8" t="n">
-        <v>19.73848560234166</v>
+        <v>3.207503910380519</v>
       </c>
       <c r="E8" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F8" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.41236509134907</v>
+        <v>6.079509327344224</v>
       </c>
       <c r="D9" t="n">
-        <v>25.5436599212636</v>
+        <v>4.150844737205336</v>
       </c>
       <c r="E9" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F9" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.82803001212606</v>
+        <v>2.734554876970485</v>
       </c>
       <c r="D10" t="n">
-        <v>16.63658406640836</v>
+        <v>2.703444910791358</v>
       </c>
       <c r="E10" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F10" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.2195898274088</v>
+        <v>2.635683346953931</v>
       </c>
       <c r="D11" t="n">
-        <v>12.75582710820687</v>
+        <v>2.072821905083616</v>
       </c>
       <c r="E11" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F11" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>61.54568021384108</v>
+        <v>10.00117303474918</v>
       </c>
       <c r="D12" t="n">
-        <v>23.25940669922602</v>
+        <v>3.779653588624228</v>
       </c>
       <c r="E12" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F12" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.74802872306388</v>
+        <v>7.921554667497881</v>
       </c>
       <c r="D13" t="n">
-        <v>48.04526641485387</v>
+        <v>7.807355792413754</v>
       </c>
       <c r="E13" t="n">
-        <v>15.52936919476516</v>
+        <v>2.523522494149338</v>
       </c>
       <c r="F13" t="n">
-        <v>10.13214005105254</v>
+        <v>1.646472758296038</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
